--- a/DesignData/Excel_Masters/StageWaveDetail_Master.xlsx
+++ b/DesignData/Excel_Masters/StageWaveDetail_Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\Excel_Masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\Unreal Projects\ProjectParadise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="55">
   <si>
     <t>---</t>
   </si>
@@ -40,11 +40,150 @@
   </si>
   <si>
     <t>TargetStageID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>MonsterID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage1_1</t>
+  </si>
+  <si>
+    <t>DanceMakane</t>
+  </si>
+  <si>
+    <t>Spawn.C</t>
+  </si>
+  <si>
+    <t>Fiti</t>
+  </si>
+  <si>
+    <t>Spawn.B</t>
+  </si>
+  <si>
+    <t>BombSpider</t>
+  </si>
+  <si>
+    <t>Spawn.A</t>
+  </si>
+  <si>
+    <t>Jellyfish</t>
+  </si>
+  <si>
+    <t>Stage1_2</t>
+  </si>
+  <si>
+    <t>Pufferfish</t>
+  </si>
+  <si>
+    <t>Spawn.D</t>
+  </si>
+  <si>
+    <t>Stage1_3</t>
+  </si>
+  <si>
+    <t>Makane</t>
+  </si>
+  <si>
+    <t>Spawn.Center</t>
+  </si>
+  <si>
+    <t>Wolfron</t>
+  </si>
+  <si>
+    <t>Stage1_4</t>
+  </si>
+  <si>
+    <t>HoneyMos</t>
+  </si>
+  <si>
+    <t>GhostMacaron</t>
+  </si>
+  <si>
+    <t>Stage1_5</t>
+  </si>
+  <si>
+    <t>GuardianTreant</t>
+  </si>
+  <si>
+    <t>Stage1_6</t>
+  </si>
+  <si>
+    <t>Stage1_7</t>
+  </si>
+  <si>
+    <t>Stage1_8</t>
+  </si>
+  <si>
+    <t>Stage1_9</t>
+  </si>
+  <si>
+    <t>Stage1_10</t>
+  </si>
+  <si>
+    <t>Bearking</t>
+  </si>
+  <si>
+    <t>Stage2_1</t>
+  </si>
+  <si>
+    <t>FelicisMachine</t>
+  </si>
+  <si>
+    <t>Deatheye</t>
+  </si>
+  <si>
+    <t>HackingTool</t>
+  </si>
+  <si>
+    <t>Stage2_2</t>
+  </si>
+  <si>
+    <t>DieS</t>
+  </si>
+  <si>
+    <t>Mechanicus</t>
+  </si>
+  <si>
+    <t>Stage2_3</t>
+  </si>
+  <si>
+    <t>Cursedmass</t>
+  </si>
+  <si>
+    <t>Stage2_4</t>
+  </si>
+  <si>
+    <t>Watcher</t>
+  </si>
+  <si>
+    <t>Stage2_5</t>
+  </si>
+  <si>
+    <t>Weaponmaster</t>
+  </si>
+  <si>
+    <t>Stage2_6</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>Stage2_7</t>
+  </si>
+  <si>
+    <t>Stage2_8</t>
+  </si>
+  <si>
+    <t>Stage2_9</t>
+  </si>
+  <si>
+    <t>BronzeGear</t>
+  </si>
+  <si>
+    <t>Stage2_10</t>
+  </si>
+  <si>
+    <t>Balrog</t>
   </si>
 </sst>
 </file>
@@ -962,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -989,6 +1128,1774 @@
       </c>
       <c r="H1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>0.7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>0.6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>0.7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>0.7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>0.7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>0.6</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>0.6</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <v>6</v>
+      </c>
+      <c r="G12">
+        <v>0.7</v>
+      </c>
+      <c r="H12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>1.2</v>
+      </c>
+      <c r="H13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>7</v>
+      </c>
+      <c r="E14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>0.7</v>
+      </c>
+      <c r="H14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15">
+        <v>0.6</v>
+      </c>
+      <c r="H15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17">
+        <v>6</v>
+      </c>
+      <c r="G17">
+        <v>0.9</v>
+      </c>
+      <c r="H17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18">
+        <v>6</v>
+      </c>
+      <c r="G18">
+        <v>0.9</v>
+      </c>
+      <c r="H18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19">
+        <v>6</v>
+      </c>
+      <c r="G19">
+        <v>0.9</v>
+      </c>
+      <c r="H19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
+        <v>1.3</v>
+      </c>
+      <c r="H20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>0.7</v>
+      </c>
+      <c r="H22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23">
+        <v>1.4</v>
+      </c>
+      <c r="H23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24">
+        <v>0.6</v>
+      </c>
+      <c r="H24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25">
+        <v>4</v>
+      </c>
+      <c r="G25">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <v>1.4</v>
+      </c>
+      <c r="H26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27">
+        <v>0.9</v>
+      </c>
+      <c r="H27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>7</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28">
+        <v>0.8</v>
+      </c>
+      <c r="H28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31">
+        <v>0.6</v>
+      </c>
+      <c r="H31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32">
+        <v>1.3</v>
+      </c>
+      <c r="H32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33">
+        <v>1.5</v>
+      </c>
+      <c r="H33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34">
+        <v>7</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34">
+        <v>4</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35">
+        <v>0.9</v>
+      </c>
+      <c r="H35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36" t="s">
+        <v>33</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38">
+        <v>1.2</v>
+      </c>
+      <c r="H38" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39" t="s">
+        <v>36</v>
+      </c>
+      <c r="F39">
+        <v>6</v>
+      </c>
+      <c r="G39">
+        <v>0.8</v>
+      </c>
+      <c r="H39" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40" t="s">
+        <v>37</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40">
+        <v>1.4</v>
+      </c>
+      <c r="H40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41" t="s">
+        <v>39</v>
+      </c>
+      <c r="F41">
+        <v>5</v>
+      </c>
+      <c r="G41">
+        <v>0.9</v>
+      </c>
+      <c r="H41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42">
+        <v>7</v>
+      </c>
+      <c r="E42" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42">
+        <v>3</v>
+      </c>
+      <c r="G42">
+        <v>0.8</v>
+      </c>
+      <c r="H42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43" t="s">
+        <v>36</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44">
+        <v>5</v>
+      </c>
+      <c r="E44" t="s">
+        <v>37</v>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+      <c r="G44">
+        <v>1.4</v>
+      </c>
+      <c r="H44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45">
+        <v>6</v>
+      </c>
+      <c r="G45">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <v>7</v>
+      </c>
+      <c r="E46" t="s">
+        <v>40</v>
+      </c>
+      <c r="F46">
+        <v>6</v>
+      </c>
+      <c r="G46">
+        <v>0.6</v>
+      </c>
+      <c r="H46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+      <c r="G47">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H47" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48">
+        <v>3</v>
+      </c>
+      <c r="G48">
+        <v>0.8</v>
+      </c>
+      <c r="H48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>43</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49">
+        <v>7</v>
+      </c>
+      <c r="E49" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49">
+        <v>1.5</v>
+      </c>
+      <c r="H49" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>43</v>
+      </c>
+      <c r="C50">
+        <v>3</v>
+      </c>
+      <c r="D50">
+        <v>7</v>
+      </c>
+      <c r="E50" t="s">
+        <v>42</v>
+      </c>
+      <c r="F50">
+        <v>4</v>
+      </c>
+      <c r="G50">
+        <v>0.7</v>
+      </c>
+      <c r="H50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51" t="s">
+        <v>35</v>
+      </c>
+      <c r="F51">
+        <v>6</v>
+      </c>
+      <c r="G51">
+        <v>1.5</v>
+      </c>
+      <c r="H51" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52" t="s">
+        <v>46</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+      <c r="E53" t="s">
+        <v>39</v>
+      </c>
+      <c r="F53">
+        <v>6</v>
+      </c>
+      <c r="G53">
+        <v>1.2</v>
+      </c>
+      <c r="H53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>5</v>
+      </c>
+      <c r="E54" t="s">
+        <v>48</v>
+      </c>
+      <c r="F54">
+        <v>6</v>
+      </c>
+      <c r="G54">
+        <v>0.5</v>
+      </c>
+      <c r="H54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>47</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55">
+        <v>5</v>
+      </c>
+      <c r="E55" t="s">
+        <v>39</v>
+      </c>
+      <c r="F55">
+        <v>5</v>
+      </c>
+      <c r="G55">
+        <v>0.5</v>
+      </c>
+      <c r="H55" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56">
+        <v>3</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56" t="s">
+        <v>39</v>
+      </c>
+      <c r="F56">
+        <v>5</v>
+      </c>
+      <c r="G56">
+        <v>0.5</v>
+      </c>
+      <c r="H56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>49</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57" t="s">
+        <v>36</v>
+      </c>
+      <c r="F57">
+        <v>4</v>
+      </c>
+      <c r="G57">
+        <v>1.3</v>
+      </c>
+      <c r="H57" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>49</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58">
+        <v>5</v>
+      </c>
+      <c r="E58" t="s">
+        <v>48</v>
+      </c>
+      <c r="F58">
+        <v>6</v>
+      </c>
+      <c r="G58">
+        <v>1.3</v>
+      </c>
+      <c r="H58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>49</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59" t="s">
+        <v>37</v>
+      </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="G59">
+        <v>1.3</v>
+      </c>
+      <c r="H59" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>49</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
+      <c r="D60">
+        <v>7</v>
+      </c>
+      <c r="E60" t="s">
+        <v>39</v>
+      </c>
+      <c r="F60">
+        <v>5</v>
+      </c>
+      <c r="G60">
+        <v>1.4</v>
+      </c>
+      <c r="H60" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>50</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61" t="s">
+        <v>44</v>
+      </c>
+      <c r="F61">
+        <v>4</v>
+      </c>
+      <c r="G61">
+        <v>1.3</v>
+      </c>
+      <c r="H61" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>50</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <v>7</v>
+      </c>
+      <c r="E62" t="s">
+        <v>36</v>
+      </c>
+      <c r="F62">
+        <v>3</v>
+      </c>
+      <c r="G62">
+        <v>1.4</v>
+      </c>
+      <c r="H62" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>50</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63" t="s">
+        <v>42</v>
+      </c>
+      <c r="F63">
+        <v>5</v>
+      </c>
+      <c r="G63">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H63" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>50</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>5</v>
+      </c>
+      <c r="E64" t="s">
+        <v>42</v>
+      </c>
+      <c r="F64">
+        <v>6</v>
+      </c>
+      <c r="G64">
+        <v>0.9</v>
+      </c>
+      <c r="H64" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>51</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>3</v>
+      </c>
+      <c r="E65" t="s">
+        <v>52</v>
+      </c>
+      <c r="F65">
+        <v>5</v>
+      </c>
+      <c r="G65">
+        <v>0.8</v>
+      </c>
+      <c r="H65" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>51</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="D66">
+        <v>7</v>
+      </c>
+      <c r="E66" t="s">
+        <v>48</v>
+      </c>
+      <c r="F66">
+        <v>4</v>
+      </c>
+      <c r="G66">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H66" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>51</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67">
+        <v>5</v>
+      </c>
+      <c r="E67" t="s">
+        <v>37</v>
+      </c>
+      <c r="F67">
+        <v>6</v>
+      </c>
+      <c r="G67">
+        <v>0.7</v>
+      </c>
+      <c r="H67" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>51</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68" t="s">
+        <v>35</v>
+      </c>
+      <c r="F68">
+        <v>3</v>
+      </c>
+      <c r="G68">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H68" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>3</v>
+      </c>
+      <c r="E69" t="s">
+        <v>54</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1002,5 +2909,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DesignData/Excel_Masters/StageWaveDetail_Master.xlsx
+++ b/DesignData/Excel_Masters/StageWaveDetail_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23745" windowHeight="8040"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19965" windowHeight="10965"/>
   </bookViews>
   <sheets>
     <sheet name="StageWaveDetail" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="80">
   <si>
     <t>---</t>
   </si>
   <si>
+    <t>TargetStageID</t>
+  </si>
+  <si>
     <t>WaveOrder</t>
   </si>
   <si>
     <t>PreWaveDelay</t>
   </si>
   <si>
+    <t>MonsterID</t>
+  </si>
+  <si>
     <t>SpawnCount</t>
   </si>
   <si>
@@ -39,12 +45,6 @@
     <t>SpawnPointTag</t>
   </si>
   <si>
-    <t>TargetStageID</t>
-  </si>
-  <si>
-    <t>MonsterID</t>
-  </si>
-  <si>
     <t>Stage1_1</t>
   </si>
   <si>
@@ -184,6 +184,81 @@
   </si>
   <si>
     <t>Balrog</t>
+  </si>
+  <si>
+    <t>DoctorMacaron</t>
+  </si>
+  <si>
+    <t>Hanged_Macaron</t>
+  </si>
+  <si>
+    <t>Karakasa</t>
+  </si>
+  <si>
+    <t>LikeStatue</t>
+  </si>
+  <si>
+    <t>MaskScarecrow</t>
+  </si>
+  <si>
+    <t>Mandragora</t>
+  </si>
+  <si>
+    <t>PistolShrimp</t>
+  </si>
+  <si>
+    <t>Octopus</t>
+  </si>
+  <si>
+    <t>KrakenTentacle</t>
+  </si>
+  <si>
+    <t>Kraken</t>
+  </si>
+  <si>
+    <t>FelicisShinobi</t>
+  </si>
+  <si>
+    <t>TinWoodman</t>
+  </si>
+  <si>
+    <t>Gemini_Scythe</t>
+  </si>
+  <si>
+    <t>Graf</t>
+  </si>
+  <si>
+    <t>Mimic</t>
+  </si>
+  <si>
+    <t>SharkRider</t>
+  </si>
+  <si>
+    <t>SoundPro</t>
+  </si>
+  <si>
+    <t>Starspawn</t>
+  </si>
+  <si>
+    <t>Famine</t>
+  </si>
+  <si>
+    <t>Seasoner</t>
+  </si>
+  <si>
+    <t>Ushabti</t>
+  </si>
+  <si>
+    <t>Wagon</t>
+  </si>
+  <si>
+    <t>Leechking</t>
+  </si>
+  <si>
+    <t>Megaron</t>
+  </si>
+  <si>
+    <t>LordFelice</t>
   </si>
 </sst>
 </file>
@@ -1101,7 +1176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -1109,25 +1184,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -1170,7 +1245,7 @@
         <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -1196,7 +1271,7 @@
         <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1222,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -1248,7 +1323,7 @@
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>6</v>
@@ -1300,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F8">
         <v>6</v>
@@ -1326,7 +1401,7 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="F9">
         <v>3</v>
@@ -1352,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -1378,7 +1453,7 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>3</v>
@@ -1404,7 +1479,7 @@
         <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F12">
         <v>6</v>
@@ -1430,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -1456,10 +1531,10 @@
         <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>0.7</v>
@@ -1473,25 +1548,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H15" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -1505,19 +1580,19 @@
         <v>1</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F16">
         <v>3</v>
       </c>
       <c r="G16">
-        <v>1.1000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -1528,22 +1603,22 @@
         <v>23</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>0.9</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -1557,10 +1632,10 @@
         <v>2</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F18">
         <v>6</v>
@@ -1569,7 +1644,7 @@
         <v>0.9</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -1580,13 +1655,13 @@
         <v>23</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F19">
         <v>6</v>
@@ -1595,7 +1670,7 @@
         <v>0.9</v>
       </c>
       <c r="H19" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -1609,19 +1684,19 @@
         <v>3</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="H20" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -1629,25 +1704,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -1655,7 +1730,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1664,13 +1739,13 @@
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="H22" t="s">
         <v>21</v>
@@ -1684,19 +1759,19 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F23">
         <v>3</v>
       </c>
       <c r="G23">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H23" t="s">
         <v>21</v>
@@ -1710,22 +1785,22 @@
         <v>28</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="H24" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -1733,25 +1808,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F25">
         <v>4</v>
       </c>
       <c r="G25">
-        <v>1.1000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H25" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -1762,22 +1837,22 @@
         <v>29</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E26" t="s">
         <v>25</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26">
-        <v>1.4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H26" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -1791,16 +1866,16 @@
         <v>2</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="H27" t="s">
         <v>10</v>
@@ -1814,22 +1889,22 @@
         <v>29</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -1837,25 +1912,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H29" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -1866,22 +1941,22 @@
         <v>30</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="F30">
         <v>4</v>
       </c>
       <c r="G30">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -1889,22 +1964,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E31" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F31">
         <v>4</v>
       </c>
       <c r="G31">
-        <v>0.6</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H31" t="s">
         <v>21</v>
@@ -1915,25 +1990,25 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H32" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
@@ -1941,25 +2016,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
@@ -1970,19 +2045,19 @@
         <v>31</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="F34">
         <v>4</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H34" t="s">
         <v>21</v>
@@ -1996,22 +2071,22 @@
         <v>31</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G35">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="H35" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -2019,25 +2094,25 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H36" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
@@ -2045,25 +2120,25 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E37" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -2071,25 +2146,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="H38" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
@@ -2097,25 +2172,25 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="F39">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -2126,22 +2201,22 @@
         <v>34</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G40">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -2149,25 +2224,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E41" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="F41">
         <v>5</v>
       </c>
       <c r="G41">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H41" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
@@ -2175,25 +2250,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E42" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G42">
         <v>0.8</v>
       </c>
       <c r="H42" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -2201,22 +2276,22 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="H43" t="s">
         <v>14</v>
@@ -2230,22 +2305,22 @@
         <v>38</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F44">
         <v>5</v>
       </c>
       <c r="G44">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="H44" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
@@ -2253,25 +2328,25 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E45" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F45">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G45">
-        <v>1.1000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H45" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
@@ -2279,22 +2354,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
       <c r="D46">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G46">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H46" t="s">
         <v>14</v>
@@ -2305,22 +2380,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E47" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G47">
-        <v>1.1000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="H47" t="s">
         <v>14</v>
@@ -2331,25 +2406,25 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C48">
         <v>1</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G48">
-        <v>0.8</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H48" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
@@ -2357,7 +2432,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -2366,16 +2441,16 @@
         <v>7</v>
       </c>
       <c r="E49" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G49">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="H49" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
@@ -2383,22 +2458,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C50">
         <v>3</v>
       </c>
       <c r="D50">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E50" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H50" t="s">
         <v>21</v>
@@ -2412,19 +2487,19 @@
         <v>43</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>1.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H51" t="s">
         <v>14</v>
@@ -2435,25 +2510,25 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H52" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
@@ -2461,25 +2536,25 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E53" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="F53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G53">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="H53" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
@@ -2487,25 +2562,25 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E54" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="F54">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G54">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H54" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
@@ -2513,22 +2588,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G55">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="H55" t="s">
         <v>14</v>
@@ -2539,25 +2614,25 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D56">
+        <v>3</v>
+      </c>
+      <c r="E56" t="s">
+        <v>73</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
         <v>0</v>
       </c>
-      <c r="E56" t="s">
-        <v>39</v>
-      </c>
-      <c r="F56">
-        <v>5</v>
-      </c>
-      <c r="G56">
-        <v>0.5</v>
-      </c>
       <c r="H56" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
@@ -2565,7 +2640,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -2574,16 +2649,16 @@
         <v>3</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="F57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G57">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="H57" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
@@ -2591,7 +2666,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -2600,16 +2675,16 @@
         <v>5</v>
       </c>
       <c r="E58" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F58">
         <v>6</v>
       </c>
       <c r="G58">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="H58" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
@@ -2617,25 +2692,25 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E59" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G59">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="H59" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
@@ -2643,22 +2718,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C60">
         <v>3</v>
       </c>
       <c r="D60">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="F60">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G60">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
@@ -2669,7 +2744,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -2678,16 +2753,16 @@
         <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G61">
         <v>1.3</v>
       </c>
       <c r="H61" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
@@ -2695,25 +2770,25 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C62">
         <v>2</v>
       </c>
       <c r="D62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G62">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H62" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
@@ -2721,7 +2796,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -2730,16 +2805,16 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="F63">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G63">
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="H63" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
@@ -2747,25 +2822,25 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C64">
         <v>3</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E64" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G64">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="H64" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
@@ -2773,7 +2848,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -2782,16 +2857,16 @@
         <v>3</v>
       </c>
       <c r="E65" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G65">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="H65" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
@@ -2799,7 +2874,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C66">
         <v>2</v>
@@ -2808,16 +2883,16 @@
         <v>7</v>
       </c>
       <c r="E66" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="F66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G66">
-        <v>1.1000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="H66" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -2825,25 +2900,25 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="F67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G67">
-        <v>0.7</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H67" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -2851,25 +2926,25 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E68" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G68">
-        <v>1.1000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="H68" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -2877,38 +2952,133 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>51</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>3</v>
+      </c>
+      <c r="E69" t="s">
+        <v>44</v>
+      </c>
+      <c r="F69">
+        <v>5</v>
+      </c>
+      <c r="G69">
+        <v>0.8</v>
+      </c>
+      <c r="H69" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>51</v>
+      </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
+      <c r="D70">
+        <v>7</v>
+      </c>
+      <c r="E70" t="s">
+        <v>78</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H70" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>51</v>
+      </c>
+      <c r="C71">
+        <v>3</v>
+      </c>
+      <c r="D71">
+        <v>5</v>
+      </c>
+      <c r="E71" t="s">
+        <v>79</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>0.7</v>
+      </c>
+      <c r="H71" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>51</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72" t="s">
+        <v>35</v>
+      </c>
+      <c r="F72">
+        <v>3</v>
+      </c>
+      <c r="G72">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H72" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
         <v>53</v>
       </c>
-      <c r="C69">
-        <v>1</v>
-      </c>
-      <c r="D69">
-        <v>3</v>
-      </c>
-      <c r="E69" t="s">
-        <v>54</v>
-      </c>
-      <c r="F69">
-        <v>1</v>
-      </c>
-      <c r="G69">
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73" t="s">
+        <v>46</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
         <v>0</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H73" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류" error="음수(-)는 입력할 수 없습니다. 0 이상의 숫자를 입력해주세요." sqref="D1:D1048576 G1:G1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류" error="음수(-)와 0은 입력할 수 없습니다. 0 보다 큰 숫자를 입력해주세요." sqref="F1:F1048576 C1:C1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>